--- a/TestData/LV_TMTT0037504_VerifyTheTASDNDFunctionalityforFVAOpportunityAndEngagementOnSFLightningView.xlsx
+++ b/TestData/LV_TMTT0037504_VerifyTheTASDNDFunctionalityforFVAOpportunityAndEngagementOnSFLightningView.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD9FF29-268D-47BB-B63C-F25DE7AE461C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F64CDC-A622-4163-BF0A-8AE73EDA88AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -161,9 +161,6 @@
     <t>Techno Coatings, Inc.</t>
   </si>
   <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -396,6 +393,9 @@
   </si>
   <si>
     <t>Dimitri Drone</t>
+  </si>
+  <si>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>
@@ -812,14 +812,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -827,18 +827,18 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -849,13 +849,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B72C63D9-9284-4C4B-9F1D-16D1550F550E}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
     </row>
@@ -867,14 +867,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204DA895-5616-4092-9340-8DD85852997B}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -882,26 +882,26 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -912,17 +912,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -935,24 +935,24 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -964,28 +964,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.33203125" customWidth="1"/>
+    <col min="26" max="26" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>33</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>34</v>
@@ -1071,13 +1071,13 @@
         <v>35</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -1085,88 +1085,88 @@
         <v>37</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E2" t="s">
         <v>38</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>39</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" t="s">
         <v>40</v>
       </c>
-      <c r="G2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" t="s">
+        <v>69</v>
+      </c>
+      <c r="L2" t="s">
         <v>41</v>
       </c>
-      <c r="I2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="R2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U2" t="s">
+        <v>46</v>
+      </c>
+      <c r="V2" t="s">
+        <v>47</v>
+      </c>
+      <c r="W2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X2" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y2" t="s">
         <v>70</v>
       </c>
-      <c r="L2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N2" t="s">
-        <v>95</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S2" t="s">
-        <v>45</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="U2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V2" t="s">
-        <v>48</v>
-      </c>
-      <c r="W2" t="s">
-        <v>49</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>50</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="Z2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="AB2" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AC2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AD2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1179,140 +1179,140 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD3AFCB-FF3D-4430-A7EF-EB1CDD64D866}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.88671875" customWidth="1"/>
-    <col min="14" max="14" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="33" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
       <c r="C3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>101</v>
-      </c>
-      <c r="D3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>102</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" t="s">
         <v>113</v>
       </c>
-      <c r="E5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" t="s">
         <v>103</v>
       </c>
-      <c r="B6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" t="s">
-        <v>104</v>
-      </c>
       <c r="D6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" t="s">
         <v>113</v>
       </c>
-      <c r="E6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1323,64 +1323,64 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C57A28D-BDAE-4AE1-A126-325DE86B36F7}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" t="s">
         <v>113</v>
-      </c>
-      <c r="E3" t="s">
-        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1391,68 +1391,68 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>59</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>60</v>
-      </c>
-      <c r="D2" t="s">
-        <v>61</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1463,224 +1463,224 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF5C07A2-98E8-49FB-8166-32C99B1B07D9}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>91</v>
-      </c>
       <c r="B2" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E2">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>92</v>
-      </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>92</v>
-      </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>92</v>
-      </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>92</v>
-      </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E7">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>92</v>
-      </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E8">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>92</v>
-      </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E9">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>92</v>
-      </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E10">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>92</v>
-      </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E11">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>92</v>
-      </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E12">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>92</v>
-      </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E13">
         <v>10</v>

--- a/TestData/LV_TMTT0037504_VerifyTheTASDNDFunctionalityforFVAOpportunityAndEngagementOnSFLightningView.xlsx
+++ b/TestData/LV_TMTT0037504_VerifyTheTASDNDFunctionalityforFVAOpportunityAndEngagementOnSFLightningView.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F64CDC-A622-4163-BF0A-8AE73EDA88AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF0762B-DD10-4239-8300-7657268F198D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="116">
   <si>
     <t>User</t>
   </si>
@@ -327,9 +327,6 @@
   </si>
   <si>
     <t>TAS - Due Diligence Services</t>
-  </si>
-  <si>
-    <t>Kiran Lulla</t>
   </si>
   <si>
     <t>Dept.</t>
@@ -814,7 +811,7 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -827,12 +824,12 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -1085,10 +1082,10 @@
         <v>37</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E2" t="s">
         <v>38</v>
@@ -1118,7 +1115,7 @@
         <v>42</v>
       </c>
       <c r="N2" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>43</v>
@@ -1198,24 +1195,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -1224,83 +1221,83 @@
         <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" t="s">
         <v>112</v>
-      </c>
-      <c r="E5" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" t="s">
         <v>102</v>
       </c>
-      <c r="B6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C6" t="s">
-        <v>103</v>
-      </c>
       <c r="D6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" t="s">
         <v>112</v>
-      </c>
-      <c r="E6" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
@@ -1309,10 +1306,10 @@
         <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -1334,24 +1331,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -1360,15 +1357,15 @@
         <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -1377,10 +1374,10 @@
         <v>70</v>
       </c>
       <c r="D3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" t="s">
         <v>112</v>
-      </c>
-      <c r="E3" t="s">
-        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0037504_VerifyTheTASDNDFunctionalityforFVAOpportunityAndEngagementOnSFLightningView.xlsx
+++ b/TestData/LV_TMTT0037504_VerifyTheTASDNDFunctionalityforFVAOpportunityAndEngagementOnSFLightningView.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF0762B-DD10-4239-8300-7657268F198D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7745854A-E6E4-4AF6-A97E-4677DA984249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="118">
   <si>
     <t>User</t>
   </si>
@@ -393,6 +393,12 @@
   </si>
   <si>
     <t>Business Services</t>
+  </si>
+  <si>
+    <t>Ashley Choi</t>
+  </si>
+  <si>
+    <t>Hussain Kazim</t>
   </si>
 </sst>
 </file>
@@ -809,14 +815,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -827,7 +833,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -846,13 +852,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B72C63D9-9284-4C4B-9F1D-16D1550F550E}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
     </row>
@@ -864,14 +870,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204DA895-5616-4092-9340-8DD85852997B}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -882,7 +888,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>72</v>
       </c>
@@ -893,7 +899,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -909,17 +915,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -932,22 +938,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -961,28 +967,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.28515625" customWidth="1"/>
+    <col min="26" max="26" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -1074,7 +1080,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -1176,24 +1182,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD3AFCB-FF3D-4430-A7EF-EB1CDD64D866}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" customWidth="1"/>
-    <col min="14" max="14" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.88671875" customWidth="1"/>
+    <col min="14" max="14" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="33" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>105</v>
       </c>
@@ -1210,9 +1216,9 @@
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -1227,7 +1233,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>98</v>
       </c>
@@ -1244,7 +1250,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>103</v>
       </c>
@@ -1261,7 +1267,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>100</v>
       </c>
@@ -1278,7 +1284,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>101</v>
       </c>
@@ -1295,7 +1301,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>104</v>
       </c>
@@ -1320,16 +1326,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C57A28D-BDAE-4AE1-A126-325DE86B36F7}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>105</v>
       </c>
@@ -1346,7 +1352,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>113</v>
       </c>
@@ -1363,9 +1369,9 @@
         <v>109</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -1388,19 +1394,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>51</v>
       </c>
@@ -1426,7 +1432,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1460,15 +1466,15 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF5C07A2-98E8-49FB-8166-32C99B1B07D9}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>86</v>
       </c>
@@ -1482,7 +1488,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>90</v>
       </c>
@@ -1499,7 +1505,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>90</v>
       </c>
@@ -1513,7 +1519,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>90</v>
       </c>
@@ -1530,7 +1536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>90</v>
       </c>
@@ -1547,7 +1553,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>90</v>
       </c>
@@ -1564,7 +1570,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
         <v>90</v>
       </c>
@@ -1581,7 +1587,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>90</v>
       </c>
@@ -1598,7 +1604,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>90</v>
       </c>
@@ -1615,7 +1621,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>90</v>
       </c>
@@ -1632,7 +1638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>90</v>
       </c>
@@ -1649,7 +1655,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
         <v>90</v>
       </c>
@@ -1666,7 +1672,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
         <v>90</v>
       </c>

--- a/TestData/LV_TMTT0037504_VerifyTheTASDNDFunctionalityforFVAOpportunityAndEngagementOnSFLightningView.xlsx
+++ b/TestData/LV_TMTT0037504_VerifyTheTASDNDFunctionalityforFVAOpportunityAndEngagementOnSFLightningView.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7745854A-E6E4-4AF6-A97E-4677DA984249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37CC78B-9D05-4DEC-9B5E-AB483436B1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -83,9 +83,6 @@
     <t>JobType</t>
   </si>
   <si>
-    <t>IndustryGroup</t>
-  </si>
-  <si>
     <t>Sector</t>
   </si>
   <si>
@@ -392,20 +389,23 @@
     <t>Dimitri Drone</t>
   </si>
   <si>
-    <t>Business Services</t>
-  </si>
-  <si>
     <t>Ashley Choi</t>
   </si>
   <si>
     <t>Hussain Kazim</t>
+  </si>
+  <si>
+    <t>IndustryGroup/HLSector</t>
+  </si>
+  <si>
+    <t>CSDN-0000007327</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -437,16 +437,206 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="20"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="52"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color indexed="23"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="17"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color indexed="54"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color indexed="54"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="54"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="62"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="52"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="60"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="63"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color indexed="54"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="27"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="26"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="31"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="44"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="49"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="53"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="51"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="62"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="45"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -510,12 +700,155 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="23"/>
+      </left>
+      <right style="thin">
+        <color indexed="23"/>
+      </right>
+      <top style="thin">
+        <color indexed="23"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="23"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="63"/>
+      </left>
+      <right style="double">
+        <color indexed="63"/>
+      </right>
+      <top style="double">
+        <color indexed="63"/>
+      </top>
+      <bottom style="double">
+        <color indexed="63"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="49"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="44"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="44"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="52"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="22"/>
+      </left>
+      <right style="thin">
+        <color indexed="22"/>
+      </right>
+      <top style="thin">
+        <color indexed="22"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="22"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="63"/>
+      </left>
+      <right style="thin">
+        <color indexed="63"/>
+      </right>
+      <top style="thin">
+        <color indexed="63"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="63"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="49"/>
+      </top>
+      <bottom style="double">
+        <color indexed="49"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="5" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="6" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyFont="0"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyFont="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyFont="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyFont="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyFont="0"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyFont="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyFont="0" applyFill="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="12" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFont="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyFont="0" applyBorder="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyFont="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -533,10 +866,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="43">
+    <cellStyle name="20% - Accent1 2" xfId="2" xr:uid="{41DDDC52-3D18-4148-8B87-83AC41AE8648}"/>
+    <cellStyle name="20% - Accent2 2" xfId="7" xr:uid="{B96F2A62-F6A5-42CC-B616-F915F859ED17}"/>
+    <cellStyle name="20% - Accent3 2" xfId="3" xr:uid="{95CF7BCB-D8C1-45D6-ABF7-F2E77EF7F2D8}"/>
+    <cellStyle name="20% - Accent4 2" xfId="4" xr:uid="{FA933954-EC89-4CE9-8B48-7B3EBD85DF34}"/>
+    <cellStyle name="20% - Accent5 2" xfId="5" xr:uid="{441E9EDE-F440-4C9E-B6AA-8A064AD5D6E4}"/>
+    <cellStyle name="20% - Accent6 2" xfId="6" xr:uid="{DD0192B5-A448-498E-8FCF-98C2A04C1932}"/>
+    <cellStyle name="40% - Accent1 2" xfId="9" xr:uid="{7B9FE000-822C-44D0-B297-C867695BFAC6}"/>
+    <cellStyle name="40% - Accent2 2" xfId="7" xr:uid="{C17F9943-D25A-4B62-AB48-1DAAC7BE2121}"/>
+    <cellStyle name="40% - Accent3 2" xfId="8" xr:uid="{5FD20A84-89AA-4706-89BC-785EA5E768CD}"/>
+    <cellStyle name="40% - Accent4 2" xfId="10" xr:uid="{C51B85EF-E5D4-422F-9762-56B038E03048}"/>
+    <cellStyle name="40% - Accent5 2" xfId="9" xr:uid="{F4C5CD48-942F-4215-8CEB-A20D56E6DAF2}"/>
+    <cellStyle name="40% - Accent6 2" xfId="10" xr:uid="{FDB9A9FD-282C-45FE-A6BE-2CE1E5CA7580}"/>
+    <cellStyle name="60% - Accent1 2" xfId="11" xr:uid="{EA48AEE9-BC39-4E0F-88EC-2EFA1E72DF8D}"/>
+    <cellStyle name="60% - Accent2 2" xfId="12" xr:uid="{EDBA46FB-CF71-4780-9424-287F388DB826}"/>
+    <cellStyle name="60% - Accent3 2" xfId="13" xr:uid="{40FB00F3-E08C-4349-9303-64283DED0CA7}"/>
+    <cellStyle name="60% - Accent4 2" xfId="14" xr:uid="{615320D6-3B91-4CA8-893A-F4EFC669C039}"/>
+    <cellStyle name="60% - Accent5 2" xfId="15" xr:uid="{28C901E5-2CFF-4431-9B08-1FC205250822}"/>
+    <cellStyle name="60% - Accent6 2" xfId="20" xr:uid="{650B251D-525D-41E6-A4B2-39E679229E1F}"/>
+    <cellStyle name="Accent1 2" xfId="15" xr:uid="{58FE67E1-FF85-4C32-9844-747FD3C47C4C}"/>
+    <cellStyle name="Accent2 2" xfId="16" xr:uid="{1D7D22C6-B499-49C3-9E3E-2A8F52AFC998}"/>
+    <cellStyle name="Accent3 2" xfId="17" xr:uid="{468F7594-0B51-46EA-B6E4-122F921418E2}"/>
+    <cellStyle name="Accent4 2" xfId="18" xr:uid="{5FCE2AF0-21B8-4542-936F-5F14F794D0AC}"/>
+    <cellStyle name="Accent5 2" xfId="19" xr:uid="{8BEBF24F-AF90-4999-A422-3D2DFBD46D4A}"/>
+    <cellStyle name="Accent6 2" xfId="20" xr:uid="{973FE752-FB46-492C-B0FC-B5335397A398}"/>
+    <cellStyle name="Bad 2" xfId="21" xr:uid="{BBABB37A-961A-4196-AEFF-ACA1A60C0FA5}"/>
+    <cellStyle name="Calculation 2" xfId="22" xr:uid="{065C3BF8-FBF3-4E6F-B642-90C9688B7605}"/>
+    <cellStyle name="Check Cell 2" xfId="23" xr:uid="{766B02F1-91D2-4029-BF63-CD2E0D403474}"/>
+    <cellStyle name="Explanatory Text 2" xfId="24" xr:uid="{F715AFB3-5EF0-46DE-BBCB-A06236A3ECD6}"/>
+    <cellStyle name="Good 2" xfId="25" xr:uid="{18C641CC-80B8-4A65-B87C-0B439B9A0018}"/>
+    <cellStyle name="Heading 1 2" xfId="26" xr:uid="{2A68CF77-17AD-4531-BB1B-8B07D40ED843}"/>
+    <cellStyle name="Heading 2 2" xfId="27" xr:uid="{E57EF05C-FD69-4EE9-A8C5-2205D9D86779}"/>
+    <cellStyle name="Heading 3 2" xfId="28" xr:uid="{B32258BF-9F4A-42B3-93E9-8E78BCB874A0}"/>
+    <cellStyle name="Heading 4 2" xfId="29" xr:uid="{DE23862E-8B59-43D1-84A5-BC654039327A}"/>
+    <cellStyle name="Input 2" xfId="30" xr:uid="{ECD5755E-E72A-484E-9FD9-4E457C096701}"/>
+    <cellStyle name="Linked Cell 2" xfId="31" xr:uid="{4BF45E36-24E5-44E8-A6FC-5E8793E529F5}"/>
+    <cellStyle name="Neutral 2" xfId="32" xr:uid="{B62A0F3E-D160-4B9F-B7BB-C2DFFF53A9BA}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{E099B11E-F677-4ECF-AAB2-3F4EB6BBEFE2}"/>
+    <cellStyle name="Note 2" xfId="33" xr:uid="{F3162BE0-5310-4A2D-A119-9D13F2CBBE88}"/>
+    <cellStyle name="Output 2" xfId="34" xr:uid="{9B274B4C-D816-490C-9C06-3D5FEFA51AEF}"/>
+    <cellStyle name="Title 2" xfId="35" xr:uid="{2F7495AC-F96F-46B5-AA2E-B4D671643DB6}"/>
+    <cellStyle name="Total 2" xfId="36" xr:uid="{01474107-295D-45B7-A109-49A334DF27E7}"/>
+    <cellStyle name="Warning Text 2" xfId="37" xr:uid="{9532D961-F4A0-41B1-829F-C35DF3325D2E}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -830,18 +1206,18 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -885,26 +1261,26 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -955,7 +1331,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -970,7 +1346,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
@@ -998,178 +1374,178 @@
       <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" t="s">
         <v>37</v>
       </c>
-      <c r="B2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>38</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" t="s">
         <v>39</v>
       </c>
-      <c r="G2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L2" t="s">
         <v>40</v>
       </c>
-      <c r="I2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" t="s">
+        <v>113</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="R2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U2" t="s">
+        <v>45</v>
+      </c>
+      <c r="V2" t="s">
+        <v>46</v>
+      </c>
+      <c r="W2" t="s">
+        <v>47</v>
+      </c>
+      <c r="X2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y2" t="s">
         <v>69</v>
       </c>
-      <c r="L2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" t="s">
-        <v>114</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="R2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U2" t="s">
-        <v>46</v>
-      </c>
-      <c r="V2" t="s">
-        <v>47</v>
-      </c>
-      <c r="W2" t="s">
-        <v>48</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="Z2" t="s">
         <v>49</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="Z2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="AB2" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AC2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AD2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1201,121 +1577,121 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" t="s">
         <v>111</v>
-      </c>
-      <c r="E5" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" t="s">
         <v>101</v>
       </c>
-      <c r="B6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C6" t="s">
-        <v>102</v>
-      </c>
       <c r="D6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6" t="s">
         <v>111</v>
-      </c>
-      <c r="E6" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1337,53 +1713,53 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" t="s">
         <v>111</v>
-      </c>
-      <c r="E3" t="s">
-        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -1408,54 +1784,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
         <v>58</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>59</v>
-      </c>
-      <c r="D2" t="s">
-        <v>60</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1476,30 +1852,30 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E2">
         <v>11</v>
@@ -1507,13 +1883,13 @@
     </row>
     <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3">
         <v>12</v>
@@ -1521,16 +1897,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>91</v>
-      </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1538,16 +1914,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>91</v>
-      </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -1555,16 +1931,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>91</v>
-      </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -1572,16 +1948,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>91</v>
-      </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -1589,16 +1965,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>91</v>
-      </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -1606,16 +1982,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>91</v>
-      </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E9">
         <v>6</v>
@@ -1623,16 +1999,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>91</v>
-      </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10">
         <v>7</v>
@@ -1640,16 +2016,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>91</v>
-      </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E11">
         <v>8</v>
@@ -1657,16 +2033,16 @@
     </row>
     <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>91</v>
-      </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E12">
         <v>9</v>
@@ -1674,16 +2050,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>91</v>
-      </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E13">
         <v>10</v>

--- a/TestData/LV_TMTT0037504_VerifyTheTASDNDFunctionalityforFVAOpportunityAndEngagementOnSFLightningView.xlsx
+++ b/TestData/LV_TMTT0037504_VerifyTheTASDNDFunctionalityforFVAOpportunityAndEngagementOnSFLightningView.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37CC78B-9D05-4DEC-9B5E-AB483436B1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA269BF-FF27-46C5-B166-8DBCCE217C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -398,7 +398,7 @@
     <t>IndustryGroup/HLSector</t>
   </si>
   <si>
-    <t>CSDN-0000007327</t>
+    <t>CSDN-0000002536</t>
   </si>
 </sst>
 </file>
@@ -848,7 +848,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyFont="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyFont="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -866,8 +866,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1 2" xfId="2" xr:uid="{41DDDC52-3D18-4148-8B87-83AC41AE8648}"/>
@@ -1191,14 +1189,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1209,7 +1207,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>113</v>
       </c>
@@ -1228,13 +1226,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B72C63D9-9284-4C4B-9F1D-16D1550F550E}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
     </row>
@@ -1246,14 +1244,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204DA895-5616-4092-9340-8DD85852997B}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1264,7 +1262,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>71</v>
       </c>
@@ -1275,7 +1273,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>65</v>
       </c>
@@ -1291,17 +1289,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1314,22 +1312,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>64</v>
       </c>
@@ -1343,28 +1341,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="29" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.33203125" customWidth="1"/>
+    <col min="26" max="26" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -1374,7 +1372,7 @@
       <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="1" t="s">
         <v>116</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1456,7 +1454,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -1466,7 +1464,7 @@
       <c r="C2" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" t="s">
         <v>117</v>
       </c>
       <c r="E2" t="s">
@@ -1558,24 +1556,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD3AFCB-FF3D-4430-A7EF-EB1CDD64D866}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.88671875" customWidth="1"/>
-    <col min="14" max="14" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" customWidth="1"/>
+    <col min="14" max="14" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="33" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>104</v>
       </c>
@@ -1592,7 +1590,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>115</v>
       </c>
@@ -1609,7 +1607,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>97</v>
       </c>
@@ -1626,7 +1624,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>102</v>
       </c>
@@ -1643,7 +1641,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>99</v>
       </c>
@@ -1660,7 +1658,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>100</v>
       </c>
@@ -1677,7 +1675,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>103</v>
       </c>
@@ -1702,16 +1700,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C57A28D-BDAE-4AE1-A126-325DE86B36F7}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>104</v>
       </c>
@@ -1728,7 +1726,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>112</v>
       </c>
@@ -1745,7 +1743,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>114</v>
       </c>
@@ -1770,19 +1768,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -1808,7 +1806,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -1842,15 +1840,15 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF5C07A2-98E8-49FB-8166-32C99B1B07D9}">
   <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>85</v>
       </c>
@@ -1864,7 +1862,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>89</v>
       </c>
@@ -1881,7 +1879,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>89</v>
       </c>
@@ -1895,7 +1893,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>89</v>
       </c>
@@ -1912,7 +1910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>89</v>
       </c>
@@ -1929,7 +1927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>89</v>
       </c>
@@ -1946,7 +1944,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>89</v>
       </c>
@@ -1963,7 +1961,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>89</v>
       </c>
@@ -1980,7 +1978,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>89</v>
       </c>
@@ -1997,7 +1995,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>89</v>
       </c>
@@ -2014,7 +2012,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>89</v>
       </c>
@@ -2031,7 +2029,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>89</v>
       </c>
@@ -2048,7 +2046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>89</v>
       </c>

--- a/TestData/LV_TMTT0037504_VerifyTheTASDNDFunctionalityforFVAOpportunityAndEngagementOnSFLightningView.xlsx
+++ b/TestData/LV_TMTT0037504_VerifyTheTASDNDFunctionalityforFVAOpportunityAndEngagementOnSFLightningView.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53666CA8-89C8-401F-A8C0-4C8BCCE0B796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E663A94B-2650-491E-B028-1BC22C47AD8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -260,9 +260,6 @@
     <t>10000</t>
   </si>
   <si>
-    <t>Liz Hedgcock</t>
-  </si>
-  <si>
     <t>Tombstone Permission</t>
   </si>
   <si>
@@ -405,6 +402,9 @@
   </si>
   <si>
     <t>FIN</t>
+  </si>
+  <si>
+    <t>Blaise Brunda</t>
   </si>
 </sst>
 </file>
@@ -1210,12 +1210,12 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -1270,7 +1270,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -1284,7 +1284,7 @@
         <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1379,7 +1379,7 @@
         <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>12</v>
@@ -1454,7 +1454,7 @@
         <v>34</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>35</v>
@@ -1468,10 +1468,10 @@
         <v>36</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
         <v>37</v>
@@ -1501,7 +1501,7 @@
         <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>42</v>
@@ -1546,7 +1546,7 @@
         <v>70</v>
       </c>
       <c r="AC2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AD2" t="s">
         <v>38</v>
@@ -1581,24 +1581,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>51</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -1607,83 +1607,83 @@
         <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" t="s">
         <v>110</v>
-      </c>
-      <c r="E5" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" t="s">
         <v>100</v>
       </c>
-      <c r="B6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" t="s">
-        <v>101</v>
-      </c>
       <c r="D6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" t="s">
         <v>110</v>
-      </c>
-      <c r="E6" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
@@ -1692,10 +1692,10 @@
         <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1718,27 +1718,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>51</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -1747,15 +1747,15 @@
         <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -1764,13 +1764,13 @@
         <v>69</v>
       </c>
       <c r="D3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" t="s">
         <v>110</v>
       </c>
-      <c r="E3" t="s">
-        <v>111</v>
-      </c>
       <c r="F3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1863,30 +1863,30 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E2">
         <v>11</v>
@@ -1894,10 +1894,10 @@
     </row>
     <row r="3" spans="1:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>40</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="C4" t="s">
         <v>40</v>
@@ -1925,16 +1925,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="C5" t="s">
         <v>40</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -1942,16 +1942,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="C6" t="s">
         <v>40</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -1959,16 +1959,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="C7" t="s">
         <v>40</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -1976,16 +1976,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="C8" t="s">
         <v>40</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -1993,16 +1993,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="C9" t="s">
         <v>40</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E9">
         <v>6</v>
@@ -2010,16 +2010,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="C10" t="s">
         <v>40</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E10">
         <v>7</v>
@@ -2027,16 +2027,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="C11" t="s">
         <v>40</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11">
         <v>8</v>
@@ -2044,16 +2044,16 @@
     </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="C12" t="s">
         <v>40</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E12">
         <v>9</v>
@@ -2061,16 +2061,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="C13" t="s">
         <v>40</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E13">
         <v>10</v>

--- a/TestData/LV_TMTT0037504_VerifyTheTASDNDFunctionalityforFVAOpportunityAndEngagementOnSFLightningView.xlsx
+++ b/TestData/LV_TMTT0037504_VerifyTheTASDNDFunctionalityforFVAOpportunityAndEngagementOnSFLightningView.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E663A94B-2650-491E-B028-1BC22C47AD8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10EA8D1-DF20-4F28-856C-8F9E568011F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StandardUser" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="121">
   <si>
     <t>User</t>
   </si>
@@ -405,6 +405,9 @@
   </si>
   <si>
     <t>Blaise Brunda</t>
+  </si>
+  <si>
+    <t>Amy Xia</t>
   </si>
 </sst>
 </file>
@@ -1705,7 +1708,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C57A28D-BDAE-4AE1-A126-325DE86B36F7}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -1716,7 +1719,7 @@
     <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>103</v>
       </c>
@@ -1736,7 +1739,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>111</v>
       </c>
@@ -1753,9 +1756,9 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
@@ -1771,6 +1774,9 @@
       </c>
       <c r="F3" t="s">
         <v>118</v>
+      </c>
+      <c r="G3" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
